--- a/data/raw/maestro_productos.xlsx
+++ b/data/raw/maestro_productos.xlsx
@@ -540,7 +540,7 @@
         <v>12</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>45545</v>
+        <v>45823</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
@@ -592,7 +592,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>45600</v>
+        <v>45878</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -644,7 +644,7 @@
         <v>4</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>45009</v>
+        <v>45287</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>45349</v>
+        <v>45627</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>14</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>45741</v>
+        <v>46019</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>6</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>45701</v>
+        <v>45979</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -852,7 +852,7 @@
         <v>4</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>45576</v>
+        <v>45854</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -904,7 +904,7 @@
         <v>9</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>45418</v>
+        <v>45696</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -956,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>45687</v>
+        <v>45965</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
@@ -1008,7 +1008,7 @@
         <v>12</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>45503</v>
+        <v>45781</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>45853</v>
+        <v>46131</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>11</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>45286</v>
+        <v>45564</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -1164,7 +1164,7 @@
         <v>13</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>45731</v>
+        <v>46009</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -1216,7 +1216,7 @@
         <v>7</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>45163</v>
+        <v>45441</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>13</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>45384</v>
+        <v>45662</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -1320,7 +1320,7 @@
         <v>5</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>45164</v>
+        <v>45442</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -1372,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>45094</v>
+        <v>45372</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -1424,7 +1424,7 @@
         <v>5</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>45907</v>
+        <v>46185</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>45336</v>
+        <v>45614</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         <v>13</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>45774</v>
+        <v>46052</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
@@ -1580,7 +1580,7 @@
         <v>13</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>46042</v>
+        <v>46320</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
@@ -1632,7 +1632,7 @@
         <v>15</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>45882</v>
+        <v>46160</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -1684,7 +1684,7 @@
         <v>13</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>45175</v>
+        <v>45453</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>9</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>45428</v>
+        <v>45706</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>5</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>45100</v>
+        <v>45378</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -1840,7 +1840,7 @@
         <v>5</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>45061</v>
+        <v>45339</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1892,7 +1892,7 @@
         <v>12</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>46009</v>
+        <v>46287</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>8</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>45459</v>
+        <v>45737</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -1996,7 +1996,7 @@
         <v>5</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>45680</v>
+        <v>45958</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>45816</v>
+        <v>46094</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
@@ -2100,7 +2100,7 @@
         <v>4</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>45103</v>
+        <v>45381</v>
       </c>
       <c r="L32" t="b">
         <v>1</v>
@@ -2152,7 +2152,7 @@
         <v>3</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>45496</v>
+        <v>45774</v>
       </c>
       <c r="L33" t="b">
         <v>1</v>
@@ -2204,7 +2204,7 @@
         <v>13</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>45621</v>
+        <v>45899</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -2256,7 +2256,7 @@
         <v>15</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>45438</v>
+        <v>45716</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
@@ -2308,7 +2308,7 @@
         <v>4</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>45895</v>
+        <v>46173</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
@@ -2360,7 +2360,7 @@
         <v>14</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>45941</v>
+        <v>46219</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
@@ -2412,7 +2412,7 @@
         <v>11</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>45264</v>
+        <v>45542</v>
       </c>
       <c r="L38" t="b">
         <v>1</v>
@@ -2464,7 +2464,7 @@
         <v>11</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>45805</v>
+        <v>46083</v>
       </c>
       <c r="L39" t="b">
         <v>1</v>
@@ -2516,7 +2516,7 @@
         <v>13</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>45688</v>
+        <v>45966</v>
       </c>
       <c r="L40" t="b">
         <v>1</v>
@@ -2568,7 +2568,7 @@
         <v>15</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>45634</v>
+        <v>45912</v>
       </c>
       <c r="L41" t="b">
         <v>1</v>
@@ -2620,7 +2620,7 @@
         <v>11</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>45756</v>
+        <v>46034</v>
       </c>
       <c r="L42" t="b">
         <v>1</v>
@@ -2672,7 +2672,7 @@
         <v>12</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>45351</v>
+        <v>45629</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
@@ -2724,7 +2724,7 @@
         <v>10</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>45043</v>
+        <v>45321</v>
       </c>
       <c r="L44" t="b">
         <v>1</v>
@@ -2776,7 +2776,7 @@
         <v>4</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>45799</v>
+        <v>46077</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -2828,7 +2828,7 @@
         <v>5</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>44968</v>
+        <v>45246</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2880,7 +2880,7 @@
         <v>11</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>45091</v>
+        <v>45369</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -2932,7 +2932,7 @@
         <v>7</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>45566</v>
+        <v>45844</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2984,7 +2984,7 @@
         <v>6</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>45984</v>
+        <v>46262</v>
       </c>
       <c r="L49" t="b">
         <v>1</v>
@@ -3036,7 +3036,7 @@
         <v>14</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>45918</v>
+        <v>46196</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -3088,7 +3088,7 @@
         <v>10</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>44948</v>
+        <v>45226</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
@@ -3140,7 +3140,7 @@
         <v>6</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>45897</v>
+        <v>46175</v>
       </c>
       <c r="L52" t="b">
         <v>1</v>
@@ -3192,7 +3192,7 @@
         <v>4</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>45713</v>
+        <v>45991</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
@@ -3244,7 +3244,7 @@
         <v>3</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>45464</v>
+        <v>45742</v>
       </c>
       <c r="L54" t="b">
         <v>1</v>
@@ -3296,7 +3296,7 @@
         <v>6</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>45325</v>
+        <v>45603</v>
       </c>
       <c r="L55" t="b">
         <v>1</v>
@@ -3348,7 +3348,7 @@
         <v>3</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>45452</v>
+        <v>45730</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -3400,7 +3400,7 @@
         <v>4</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>46040</v>
+        <v>46318</v>
       </c>
       <c r="L57" t="b">
         <v>1</v>
@@ -3452,7 +3452,7 @@
         <v>7</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>45044</v>
+        <v>45322</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -3504,7 +3504,7 @@
         <v>6</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>45243</v>
+        <v>45521</v>
       </c>
       <c r="L59" t="b">
         <v>1</v>
@@ -3556,7 +3556,7 @@
         <v>8</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>45828</v>
+        <v>46106</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -3608,7 +3608,7 @@
         <v>9</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>45291</v>
+        <v>45569</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -3660,7 +3660,7 @@
         <v>14</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>45317</v>
+        <v>45595</v>
       </c>
       <c r="L62" t="b">
         <v>1</v>
@@ -3712,7 +3712,7 @@
         <v>15</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>45168</v>
+        <v>45446</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -3764,7 +3764,7 @@
         <v>6</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>45790</v>
+        <v>46068</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
@@ -3816,7 +3816,7 @@
         <v>6</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>45642</v>
+        <v>45920</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
@@ -3868,7 +3868,7 @@
         <v>5</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>45088</v>
+        <v>45366</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -3920,7 +3920,7 @@
         <v>5</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>45071</v>
+        <v>45349</v>
       </c>
       <c r="L67" t="b">
         <v>1</v>
@@ -3972,7 +3972,7 @@
         <v>4</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>45444</v>
+        <v>45722</v>
       </c>
       <c r="L68" t="b">
         <v>1</v>
@@ -4024,7 +4024,7 @@
         <v>13</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>45736</v>
+        <v>46014</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
@@ -4076,7 +4076,7 @@
         <v>4</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>45707</v>
+        <v>45985</v>
       </c>
       <c r="L70" t="b">
         <v>1</v>
@@ -4128,7 +4128,7 @@
         <v>5</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>45116</v>
+        <v>45394</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -4180,7 +4180,7 @@
         <v>7</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>45415</v>
+        <v>45693</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>45803</v>
+        <v>46081</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>14</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>45399</v>
+        <v>45677</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -4336,7 +4336,7 @@
         <v>3</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>45140</v>
+        <v>45418</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
@@ -4388,7 +4388,7 @@
         <v>14</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>45797</v>
+        <v>46075</v>
       </c>
       <c r="L76" t="b">
         <v>1</v>
@@ -4440,7 +4440,7 @@
         <v>3</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>45463</v>
+        <v>45741</v>
       </c>
       <c r="L77" t="b">
         <v>1</v>
@@ -4492,7 +4492,7 @@
         <v>13</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>45786</v>
+        <v>46064</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
@@ -4544,7 +4544,7 @@
         <v>9</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>45262</v>
+        <v>45540</v>
       </c>
       <c r="L79" t="b">
         <v>1</v>
@@ -4596,7 +4596,7 @@
         <v>12</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>45884</v>
+        <v>46162</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
@@ -4648,7 +4648,7 @@
         <v>7</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>45797</v>
+        <v>46075</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -4700,7 +4700,7 @@
         <v>13</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>45859</v>
+        <v>46137</v>
       </c>
       <c r="L82" t="b">
         <v>1</v>
@@ -4752,7 +4752,7 @@
         <v>6</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>45393</v>
+        <v>45671</v>
       </c>
       <c r="L83" t="b">
         <v>1</v>
@@ -4804,7 +4804,7 @@
         <v>9</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>45638</v>
+        <v>45916</v>
       </c>
       <c r="L84" t="b">
         <v>1</v>
@@ -4856,7 +4856,7 @@
         <v>13</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>45089</v>
+        <v>45367</v>
       </c>
       <c r="L85" t="b">
         <v>1</v>
@@ -4908,7 +4908,7 @@
         <v>11</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>45873</v>
+        <v>46151</v>
       </c>
       <c r="L86" t="b">
         <v>1</v>
@@ -4960,7 +4960,7 @@
         <v>5</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>45544</v>
+        <v>45822</v>
       </c>
       <c r="L87" t="b">
         <v>1</v>
@@ -5012,7 +5012,7 @@
         <v>4</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>45439</v>
+        <v>45717</v>
       </c>
       <c r="L88" t="b">
         <v>1</v>
@@ -5064,7 +5064,7 @@
         <v>8</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>45841</v>
+        <v>46119</v>
       </c>
       <c r="L89" t="b">
         <v>1</v>
@@ -5116,7 +5116,7 @@
         <v>5</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>45323</v>
+        <v>45601</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -5168,7 +5168,7 @@
         <v>13</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>45398</v>
+        <v>45676</v>
       </c>
       <c r="L91" t="b">
         <v>1</v>
@@ -5220,7 +5220,7 @@
         <v>5</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>45232</v>
+        <v>45510</v>
       </c>
       <c r="L92" t="b">
         <v>1</v>
@@ -5272,7 +5272,7 @@
         <v>4</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>45241</v>
+        <v>45519</v>
       </c>
       <c r="L93" t="b">
         <v>1</v>
@@ -5324,7 +5324,7 @@
         <v>14</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>45237</v>
+        <v>45515</v>
       </c>
       <c r="L94" t="b">
         <v>1</v>
@@ -5376,7 +5376,7 @@
         <v>7</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>44998</v>
+        <v>45276</v>
       </c>
       <c r="L95" t="b">
         <v>1</v>
@@ -5428,7 +5428,7 @@
         <v>9</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>45898</v>
+        <v>46176</v>
       </c>
       <c r="L96" t="b">
         <v>1</v>
@@ -5480,7 +5480,7 @@
         <v>3</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>45967</v>
+        <v>46245</v>
       </c>
       <c r="L97" t="b">
         <v>1</v>
@@ -5532,7 +5532,7 @@
         <v>8</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>45350</v>
+        <v>45628</v>
       </c>
       <c r="L98" t="b">
         <v>1</v>
@@ -5584,7 +5584,7 @@
         <v>13</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>45687</v>
+        <v>45965</v>
       </c>
       <c r="L99" t="b">
         <v>1</v>
@@ -5636,7 +5636,7 @@
         <v>11</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>45054</v>
+        <v>45332</v>
       </c>
       <c r="L100" t="b">
         <v>1</v>
@@ -5688,7 +5688,7 @@
         <v>4</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>45086</v>
+        <v>45364</v>
       </c>
       <c r="L101" t="b">
         <v>1</v>
@@ -5740,7 +5740,7 @@
         <v>14</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>46001</v>
+        <v>46279</v>
       </c>
       <c r="L102" t="b">
         <v>1</v>
@@ -5792,7 +5792,7 @@
         <v>3</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>45149</v>
+        <v>45427</v>
       </c>
       <c r="L103" t="b">
         <v>1</v>
@@ -5844,7 +5844,7 @@
         <v>8</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>45179</v>
+        <v>45457</v>
       </c>
       <c r="L104" t="b">
         <v>1</v>
@@ -5896,7 +5896,7 @@
         <v>8</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>45007</v>
+        <v>45285</v>
       </c>
       <c r="L105" t="b">
         <v>1</v>
@@ -5948,7 +5948,7 @@
         <v>13</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>45071</v>
+        <v>45349</v>
       </c>
       <c r="L106" t="b">
         <v>1</v>
@@ -6000,7 +6000,7 @@
         <v>13</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>46033</v>
+        <v>46311</v>
       </c>
       <c r="L107" t="b">
         <v>1</v>
